--- a/src/src/main/resources/template/PmOrder_export.xlsx
+++ b/src/src/main/resources/template/PmOrder_export.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gaolei/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503156711\ws20200921\hc-apm-web\src\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD57B72E-4C33-7645-9F60-B4A059D79E3D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FEE0E47-AD17-4A94-A1F7-24974EB46BB3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="1460" windowWidth="27560" windowHeight="16040" xr2:uid="{A79E8308-D8A1-504E-B750-D626931FDE37}"/>
+    <workbookView xWindow="28560" yWindow="-16515" windowWidth="29040" windowHeight="15840" xr2:uid="{A79E8308-D8A1-504E-B750-D626931FDE37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,20 +24,121 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+  <si>
+    <t>资产名称</t>
+  </si>
+  <si>
+    <t>制造商序列号</t>
+  </si>
+  <si>
+    <t>设备编号(院方)</t>
+  </si>
+  <si>
+    <t>保养等级</t>
+  </si>
+  <si>
+    <t>保养类型</t>
+  </si>
+  <si>
+    <t>所属科室</t>
+  </si>
+  <si>
+    <t>保养规则</t>
+  </si>
+  <si>
+    <t>保养周期(月)</t>
+  </si>
+  <si>
+    <t>创建人</t>
+  </si>
+  <si>
+    <t>负责人</t>
+  </si>
+  <si>
+    <t>保养编号</t>
+  </si>
+  <si>
+    <t>当前处理步骤</t>
+  </si>
+  <si>
+    <t>工单类型</t>
+  </si>
+  <si>
+    <t>计划完成时间</t>
+  </si>
+  <si>
+    <t>&lt;/jx:forEach&gt;</t>
+  </si>
+  <si>
+    <t>${pm.assetName}</t>
+  </si>
+  <si>
+    <t>${pm.serialNum}</t>
+  </si>
+  <si>
+    <t>${pm.departNum}</t>
+  </si>
+  <si>
+    <t>${pm.ruleLevel}</t>
+  </si>
+  <si>
+    <t>${pm.clinicalDeptName}</t>
+  </si>
+  <si>
+    <t>${pm.pmType}</t>
+  </si>
+  <si>
+    <t>${pm.pmRuleName}</t>
+  </si>
+  <si>
+    <t>${pm.pmRulePeriod}</t>
+  </si>
+  <si>
+    <t>${pm.creatorName}</t>
+  </si>
+  <si>
+    <t>${pm.ownerName}</t>
+  </si>
+  <si>
+    <t>${pm.pmNum}</t>
+  </si>
+  <si>
+    <t>${pm.currentStepName}</t>
+  </si>
+  <si>
+    <t>${pm.intExtType}</t>
+  </si>
+  <si>
+    <t>${pm.planTime}</t>
+  </si>
+  <si>
+    <t>&lt;jx:forEach items="${list}" var="pm"&gt;</t>
+  </si>
+  <si>
+    <t>所属院区</t>
+  </si>
+  <si>
+    <t>${pm.siteName}</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -65,13 +166,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -87,7 +191,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -383,9 +487,131 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AF7D51F-7E0B-F54D-A4C4-4543C4A65912}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="21"/>
-  <sheetData/>
+  <dimension ref="A1:O4"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="20.399999999999999"/>
+  <cols>
+    <col min="1" max="1" width="30.62890625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.9609375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.29296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.29296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.62890625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.9609375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.62890625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.58984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/src/main/resources/template/PmOrder_export.xlsx
+++ b/src/src/main/resources/template/PmOrder_export.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503156711\ws20200921\hc-apm-web\src\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FEE0E47-AD17-4A94-A1F7-24974EB46BB3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35DFAAD-6293-4E01-959B-ECF1F246DBDD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28560" yWindow="-16515" windowWidth="29040" windowHeight="15840" xr2:uid="{A79E8308-D8A1-504E-B750-D626931FDE37}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{A79E8308-D8A1-504E-B750-D626931FDE37}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,104 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
-  <si>
-    <t>资产名称</t>
-  </si>
-  <si>
-    <t>制造商序列号</t>
-  </si>
-  <si>
-    <t>设备编号(院方)</t>
-  </si>
-  <si>
-    <t>保养等级</t>
-  </si>
-  <si>
-    <t>保养类型</t>
-  </si>
-  <si>
-    <t>所属科室</t>
-  </si>
-  <si>
-    <t>保养规则</t>
-  </si>
-  <si>
-    <t>保养周期(月)</t>
-  </si>
-  <si>
-    <t>创建人</t>
-  </si>
-  <si>
-    <t>负责人</t>
-  </si>
-  <si>
-    <t>保养编号</t>
-  </si>
-  <si>
-    <t>当前处理步骤</t>
-  </si>
-  <si>
-    <t>工单类型</t>
-  </si>
-  <si>
-    <t>计划完成时间</t>
-  </si>
-  <si>
-    <t>&lt;/jx:forEach&gt;</t>
-  </si>
-  <si>
-    <t>${pm.assetName}</t>
-  </si>
-  <si>
-    <t>${pm.serialNum}</t>
-  </si>
-  <si>
-    <t>${pm.departNum}</t>
-  </si>
-  <si>
-    <t>${pm.ruleLevel}</t>
-  </si>
-  <si>
-    <t>${pm.clinicalDeptName}</t>
-  </si>
-  <si>
-    <t>${pm.pmType}</t>
-  </si>
-  <si>
-    <t>${pm.pmRuleName}</t>
-  </si>
-  <si>
-    <t>${pm.pmRulePeriod}</t>
-  </si>
-  <si>
-    <t>${pm.creatorName}</t>
-  </si>
-  <si>
-    <t>${pm.ownerName}</t>
-  </si>
-  <si>
-    <t>${pm.pmNum}</t>
-  </si>
-  <si>
-    <t>${pm.currentStepName}</t>
-  </si>
-  <si>
-    <t>${pm.intExtType}</t>
-  </si>
-  <si>
-    <t>${pm.planTime}</t>
-  </si>
-  <si>
-    <t>&lt;jx:forEach items="${list}" var="pm"&gt;</t>
-  </si>
-  <si>
-    <t>所属院区</t>
-  </si>
-  <si>
-    <t>${pm.siteName}</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -487,131 +390,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AF7D51F-7E0B-F54D-A4C4-4543C4A65912}">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="20.399999999999999"/>
   <cols>
-    <col min="1" max="1" width="30.62890625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.9609375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.29296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.29296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.62890625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.9609375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.62890625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.58984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="1"/>
   </cols>
-  <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
